--- a/output/那須赤十字病院_随意契約_X線関連.xlsx
+++ b/output/那須赤十字病院_随意契約_X線関連.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -574,36 +574,36 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>X線一般撮影装置 MRAD-A80S/5Gの修理</t>
+          <t>X線循環器診断システムINFX-8000/HE保守契約の更新について</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr"/>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>栃木県大田原市中田原1081番地4那須赤十字病院管財課</t>
+          <t>栃木県大田原市中田原1081番地9那須赤十字病院管財課</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>令和6年4月24日</t>
+          <t>令和7年7月14日</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>キヤノンメディカルシステムズ株式会社栃木県宇都宮市大通1-4-24</t>
+          <t>キャノンメディカルシステムズ株式会社栃木県宇都宮市大通り1-4-24ＭＳＣビル</t>
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>2310000</v>
+        <v>9372000</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>https://www.nasu.jrc.or.jp/data/media/nasu-jrc/page/tender/pdf/2024_kouhyoukeiyaku.pdf</t>
+          <t>https://www.nasu.jrc.or.jp/data/media/zuiikeiyakuitiran2025.pdf</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>一般撮影（レントゲン）</t>
+          <t>血管撮影（CVS、アンギオ）</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -616,7 +616,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>デジタルラジオグラフィー二式</t>
+          <t>X線一般撮影装置 MRAD-A80S/5Gの修理</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr"/>
@@ -627,20 +627,20 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>令和7年8月2日</t>
+          <t>令和6年4月24日</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>コニカミノルタジャパン株式会社ヘルスケアカンパニー宇都宮営業所栃木県宇都宮市大通り2-3-1</t>
+          <t>キヤノンメディカルシステムズ株式会社栃木県宇都宮市大通1-4-24</t>
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>7700000</v>
+        <v>2310000</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>https://www.nasu.jrc.or.jp/data/media/zuiikeiyakuitiran2025.pdf</t>
+          <t>https://www.nasu.jrc.or.jp/data/media/nasu-jrc/page/tender/pdf/2024_kouhyoukeiyaku.pdf</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>製品</t>
+          <t>保守</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr"/>
@@ -658,7 +658,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>長尺リーダー撮影台</t>
+          <t>デジタルラジオグラフィー二式</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>令和8年3月2日</t>
+          <t>令和7年8月2日</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="F7" s="4" t="n">
-        <v>3300000</v>
+        <v>7700000</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
@@ -700,44 +700,254 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>デジタルラジオグラフィー</t>
+          <t>移動型デジタル式汎用一体型X線透視診断装置の定期点検契約の締結について</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr"/>
       <c r="C8" s="3" t="inlineStr">
         <is>
+          <t>栃木県大田原市中田原1081番地9那須赤十字病院管財課</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>令和7年11月6日</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>シーメンスヘルスケア株式会社埼玉県さいたま市大宮区土手町1-49-8ＧＭ大宮ビル2階</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>2100000</v>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nasu.jrc.or.jp/data/media/zuiikeiyakuitiran2025.pdf</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>回診用X線装置</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>保守</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>X線循環器診断システムINFX-8000/T7保守契約の更新について</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr"/>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>栃木県大田原市中田原1081番地9那須赤十字病院管財課</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>令和7年12月3日</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>キャノンメディカルシステムズ株式会社栃木県宇都宮市大通り1-4-24ＭＳＣビル</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>5709000</v>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nasu.jrc.or.jp/data/media/zuiikeiyakuitiran2025.pdf</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>血管撮影（CVS、アンギオ）</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>保守</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>X線循環器診断システム INFX-8000V/T7保守</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr"/>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>栃木県大田原市中田原1081番地9那須赤十字病院管財課</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>令和5年12月16日</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>キヤノンメディカルシステムズ株式会社栃木県宇都宮市大通1-4-24</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>5709000</v>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nasu.jrc.or.jp/data/media/nasu-jrc/page/tender/pdf/cedc5f5de7ee0a81ac11fca4330a2212.pdf</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>血管撮影（CVS、アンギオ）</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>保守</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>X線循環器診断システム INFX-8000V/T7保守</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr"/>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
           <t>栃木県大田原市中田原1081番地4那須赤十字病院管財課</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>令和6年12月16日</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>キヤノンメディカルシステムズ株式会社栃木県宇都宮市大通1-4-24</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>5709000</v>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nasu.jrc.or.jp/data/media/nasu-jrc/page/tender/pdf/2024_kouhyoukeiyaku.pdf</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>血管撮影（CVS、アンギオ）</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>保守</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>長尺リーダー撮影台</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr"/>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>栃木県大田原市中田原1081番地4那須赤十字病院管財課</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>令和8年3月2日</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>コニカミノルタジャパン株式会社ヘルスケアカンパニー宇都宮営業所栃木県宇都宮市大通り2-3-1</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>3300000</v>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nasu.jrc.or.jp/data/media/zuiikeiyakuitiran2025.pdf</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>一般撮影（レントゲン）</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>製品</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>デジタルラジオグラフィー</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr"/>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>栃木県大田原市中田原1081番地4那須赤十字病院管財課</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>令和7年3月3日</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>コニカミノルタジャパン株式会社ヘルスケアカンパニー宇都宮営業所栃木県宇都宮市大通り2-3-1</t>
         </is>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="F13" s="4" t="n">
         <v>4840000</v>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>https://www.nasu.jrc.or.jp/data/media/nasu-jrc/page/tender/pdf/2024_kouhyoukeiyaku.pdf</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr">
         <is>
           <t>一般撮影（レントゲン）</t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="I13" s="3" t="inlineStr">
         <is>
           <t>製品</t>
         </is>
       </c>
-      <c r="J8" s="3" t="inlineStr"/>
+      <c r="J13" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -811,13 +1021,9 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>公表された随意契約に該当なし</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="C6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -841,13 +1047,9 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>公表された随意契約に該当なし</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C8" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
